--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2021_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2021_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:21</t>
+    <t xml:space="preserve">2026-09-09 23:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2021_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2021_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:17</t>
+    <t xml:space="preserve">2026-09-17 14:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2021_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2021_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:13</t>
+    <t xml:space="preserve">2026-09-23 12:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -700,7 +700,9 @@
       <c r="C13" s="2" t="n">
         <v>14204</v>
       </c>
-      <c r="D13" s="2"/>
+      <c r="D13" s="2" t="n">
+        <v>2021</v>
+      </c>
       <c r="E13" s="2"/>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2021_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2021_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:42</t>
+    <t xml:space="preserve">2026-10-02 15:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2021_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2021_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:03</t>
+    <t xml:space="preserve">2026-10-05 11:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
